--- a/prixEpicerie.xlsx
+++ b/prixEpicerie.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dalto\OneDrive\Documents\Ecole\Programmation1\Team_Rosemarie_and_Leo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E56AF55-3844-4521-8808-E64B4A77CDAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C3835DE-4BCB-4244-97FE-2D970A25F201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{2198D66A-2FBF-4C5F-A307-23CE27175DD6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{2198D66A-2FBF-4C5F-A307-23CE27175DD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Metro" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
   <si>
     <t>Apple</t>
   </si>
@@ -478,7 +478,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -513,9 +513,50 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C57A07B-F668-49AB-9E14-5DC649963E41}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/prixEpicerie.xlsx
+++ b/prixEpicerie.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dalto\OneDrive\Documents\Ecole\Programmation1\Team_Rosemarie_and_Leo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C3835DE-4BCB-4244-97FE-2D970A25F201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435C5FFC-7C61-4824-9B36-73DE417D1669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{2198D66A-2FBF-4C5F-A307-23CE27175DD6}"/>
   </bookViews>
@@ -553,7 +553,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/prixEpicerie.xlsx
+++ b/prixEpicerie.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dalto\OneDrive\Documents\Ecole\Programmation1\Team_Rosemarie_and_Leo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435C5FFC-7C61-4824-9B36-73DE417D1669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E223B1D3-B6FE-4AD6-B06D-B72059795315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{2198D66A-2FBF-4C5F-A307-23CE27175DD6}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="8">
   <si>
     <t>Apple</t>
   </si>
@@ -55,13 +55,22 @@
   </si>
   <si>
     <t>potato</t>
+  </si>
+  <si>
+    <t>peaches</t>
+  </si>
+  <si>
+    <t>juice</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -71,6 +80,13 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -121,15 +137,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Monétaire" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -462,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1D0CAF0-E220-42F4-9499-7F81EB90A030}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -477,7 +496,7 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="3">
         <v>3</v>
       </c>
     </row>
@@ -485,7 +504,7 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="3">
         <v>3</v>
       </c>
     </row>
@@ -493,7 +512,7 @@
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="3">
         <v>4</v>
       </c>
     </row>
@@ -501,8 +520,24 @@
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="3">
         <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -513,7 +548,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C57A07B-F668-49AB-9E14-5DC649963E41}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -528,7 +563,7 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="3">
         <v>4</v>
       </c>
     </row>
@@ -536,7 +571,7 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="3">
         <v>5</v>
       </c>
     </row>
@@ -544,7 +579,7 @@
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
     </row>
@@ -552,8 +587,24 @@
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="3">
         <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
